--- a/output/pdf_financials_xlsx/ZC.xlsx
+++ b/output/pdf_financials_xlsx/ZC.xlsx
@@ -3965,34 +3965,34 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.225195</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.254328</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.647746</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.920817</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.920817</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.165236</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.239523</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>5.397757</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.397757</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.610158</v>
       </c>
     </row>
     <row r="93">
@@ -5970,7 +5970,11 @@
           <t>Prepaid and deposits 9</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -6774,7 +6778,11 @@
           <t>Share-based payment reserves 14</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -10930,7 +10938,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -14582,7 +14594,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E138" s="5" t="n">
         <v>4.225195</v>
       </c>

--- a/output/pdf_financials_xlsx/ZC.xlsx
+++ b/output/pdf_financials_xlsx/ZC.xlsx
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000482</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000382</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -846,25 +846,25 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001346</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002623</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000159</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.001249</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.001494</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.001787</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001837</v>
       </c>
     </row>
     <row r="13">
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.491286</v>
+        <v>-1.491768</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.201782</v>
+        <v>-0.202164</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1475,25 +1475,25 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-5.622919</v>
+        <v>-5.624265</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.742553</v>
+        <v>-2.745176</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>10.23708</v>
+        <v>10.236921</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-10.529746</v>
+        <v>-10.530995</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.660243</v>
+        <v>-3.661737</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>5.896089</v>
+        <v>5.894302</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>20.02541</v>
+        <v>20.023573</v>
       </c>
     </row>
     <row r="28">
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.491286</v>
+        <v>-1.491768</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.201782</v>
+        <v>-0.202164</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1553,25 +1553,25 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.622919</v>
+        <v>-5.624265</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.742553</v>
+        <v>-2.745176</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>10.23708</v>
+        <v>10.236921</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-10.529746</v>
+        <v>-10.530995</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.660243</v>
+        <v>-3.661737</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>5.896089</v>
+        <v>5.894302</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>20.02541</v>
+        <v>20.023573</v>
       </c>
     </row>
     <row r="30">
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-568.9021645417993</v>
+        <v>-569.0860399642931</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-61.45912968789501</v>
+        <v>-61.57547994480977</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -1592,25 +1592,25 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-227.8110538773003</v>
+        <v>-227.8655867059822</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-184.4021954363272</v>
+        <v>-184.5785591961632</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>459.0977053814961</v>
+        <v>459.0905747802743</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-626.9482305700901</v>
+        <v>-627.0225968786394</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-143.7904899512441</v>
+        <v>-143.8491808611064</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>273.9480965401565</v>
+        <v>273.8650677309718</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>462.5457627979923</v>
+        <v>462.503331878163</v>
       </c>
     </row>
     <row r="31">
@@ -1711,28 +1711,28 @@
         <v>0.052803</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.134918</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.28787</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.035996</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.253519</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.287584</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.047734</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.210859</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.062996</v>
       </c>
     </row>
     <row r="35">
@@ -1785,28 +1785,28 @@
         <v>0.052803</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.134918</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.28787</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.035996</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.253519</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.287584</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.047734</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.210859</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.062996</v>
       </c>
     </row>
     <row r="37">
@@ -2229,28 +2229,28 @@
         <v>6.450721</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>13.155536</v>
+        <v>13.020618</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>8.019937000000001</v>
+        <v>7.732067</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.920785</v>
+        <v>4.884789</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>18.3439</v>
+        <v>18.090381</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>10.998183</v>
+        <v>9.710599</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>8.834763000000001</v>
+        <v>8.787029</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>14.287658</v>
+        <v>14.076799</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>36.984176</v>
+        <v>34.92118</v>
       </c>
     </row>
     <row r="49">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -24808,7 +24808,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E363" s="5" t="n">

--- a/output/pdf_financials_xlsx/ZC.xlsx
+++ b/output/pdf_financials_xlsx/ZC.xlsx
@@ -1305,10 +1305,8 @@
       <c r="C23" s="3" t="n">
         <v>-0.210136</v>
       </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D23" s="3" t="n">
+        <v>5.28006</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-5.622919</v>
@@ -4219,10 +4217,8 @@
       <c r="C99" s="3" t="n">
         <v>-0.210136</v>
       </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D99" s="3" t="n">
+        <v>5.28006</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-5.622919</v>
@@ -4258,10 +4254,8 @@
       <c r="C100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
@@ -4297,10 +4291,8 @@
       <c r="C101" s="3" t="n">
         <v>-0.250306</v>
       </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D101" s="3" t="n">
+        <v>0.23191</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>-0.334074</v>
@@ -4336,10 +4328,8 @@
       <c r="C102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E102" s="3" t="n">
         <v>0</v>
@@ -4375,10 +4365,8 @@
       <c r="C103" s="3" t="n">
         <v>-0.052816</v>
       </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D103" s="3" t="n">
+        <v>0.201213</v>
       </c>
       <c r="E103" s="3" t="n">
         <v>-0.06551800000000001</v>
@@ -4414,10 +4402,8 @@
       <c r="C104" s="3" t="n">
         <v>0.238488</v>
       </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D104" s="3" t="n">
+        <v>-0.256091</v>
       </c>
       <c r="E104" s="3" t="n">
         <v>0.006287</v>
@@ -4453,10 +4439,8 @@
       <c r="C105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E105" s="3" t="n">
         <v>0</v>
@@ -4492,10 +4476,8 @@
       <c r="C106" s="3" t="n">
         <v>-0.064634</v>
       </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D106" s="3" t="n">
+        <v>0.177032</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-0.393305</v>
@@ -4531,10 +4513,8 @@
       <c r="C107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E107" s="3" t="n">
         <v>0.273071</v>
@@ -4570,10 +4550,8 @@
       <c r="C108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E108" s="3" t="n">
         <v>0</v>
@@ -4609,10 +4587,8 @@
       <c r="C109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E109" s="3" t="n">
         <v>0</v>
@@ -4648,10 +4624,8 @@
       <c r="C110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -4660,13 +4634,13 @@
         <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.004756</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.005799</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.000528</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -4687,10 +4661,8 @@
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -4726,10 +4698,8 @@
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -4765,10 +4735,8 @@
       <c r="C113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E113" s="3" t="n">
         <v>0</v>
@@ -4799,36 +4767,34 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-1.387733</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.724472</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>-2.589785</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-2.413727</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-3.062763</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-1.839074</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-3.437388</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-3.465232</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-1.470598</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-2.565921</v>
       </c>
     </row>
     <row r="115">
@@ -4843,10 +4809,8 @@
       <c r="C115" s="3" t="n">
         <v>1.955638</v>
       </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D115" s="3" t="n">
+        <v>-0.821931</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0.196306</v>
@@ -4882,10 +4846,8 @@
       <c r="C116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0</v>
@@ -4921,10 +4883,8 @@
       <c r="C117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E117" s="3" t="n">
         <v>0</v>
@@ -4960,10 +4920,8 @@
       <c r="C118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0</v>
@@ -5042,10 +5000,8 @@
       <c r="C120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E120" s="3" t="n">
         <v>0</v>
@@ -5081,10 +5037,8 @@
       <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>0</v>
@@ -5120,10 +5074,8 @@
       <c r="C122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E122" s="3" t="n">
         <v>0</v>
@@ -5159,10 +5111,8 @@
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E123" s="3" t="n">
         <v>0</v>
@@ -5198,10 +5148,8 @@
       <c r="C124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
@@ -5237,10 +5185,8 @@
       <c r="C125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -5276,10 +5222,8 @@
       <c r="C126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E126" s="3" t="n">
         <v>0</v>
@@ -5372,10 +5316,8 @@
       <c r="C128" s="3" t="n">
         <v>0.469607</v>
       </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E128" s="3" t="n">
         <v>0</v>
@@ -5454,10 +5396,8 @@
       <c r="C130" s="3" t="n">
         <v>0.114495</v>
       </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D130" s="3" t="n">
+        <v>0.124745</v>
       </c>
       <c r="E130" s="3" t="n">
         <v>0.134918</v>
@@ -5493,10 +5433,8 @@
       <c r="C131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E131" s="3" t="n">
         <v>0</v>
@@ -5532,10 +5470,8 @@
       <c r="C132" s="3" t="n">
         <v>0.061692</v>
       </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D132" s="3" t="n">
+        <v>0.010173</v>
       </c>
       <c r="E132" s="3" t="n">
         <v>0.152952</v>
@@ -5571,10 +5507,8 @@
       <c r="C133" s="3" t="n">
         <v>0.052803</v>
       </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D133" s="3" t="n">
+        <v>0.134918</v>
       </c>
       <c r="E133" s="3" t="n">
         <v>0.28787</v>
@@ -5610,10 +5544,8 @@
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -5649,10 +5581,8 @@
       <c r="C135" s="3" t="n">
         <v>-0.856553</v>
       </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D135" s="3" t="n">
+        <v>-1.533785</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-1.968044</v>
@@ -5687,7 +5617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N393"/>
+  <dimension ref="A1:N401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14858,7 +14788,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -16072,7 +16006,11 @@
           <t>Acquisition of investments</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -17018,7 +16956,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -17864,7 +17806,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -18390,7 +18336,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -18980,7 +18930,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -20829,10 +20783,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G234" s="5" t="n">
+        <v>-5.955591</v>
       </c>
       <c r="H234" s="5" t="n">
         <v>5.235542</v>
@@ -20893,10 +20845,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G235" s="5" t="n">
+        <v>-0.515351</v>
       </c>
       <c r="H235" s="5" t="n">
         <v>-0.5436260000000001</v>
@@ -20957,10 +20907,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G236" s="5" t="n">
+        <v>0.309404</v>
       </c>
       <c r="H236" s="5" t="n">
         <v>0.016787</v>
@@ -21087,10 +21035,8 @@
       <c r="F238" s="5" t="n">
         <v>1.955638</v>
       </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G238" s="5" t="n">
+        <v>-0.821931</v>
       </c>
       <c r="H238" s="5" t="n">
         <v>0.196306</v>
@@ -21345,10 +21291,8 @@
       <c r="F242" s="5" t="n">
         <v>0.028843</v>
       </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G242" s="5" t="n">
+        <v>0.049052</v>
       </c>
       <c r="H242" s="5" t="n">
         <v>0.134665</v>
@@ -21605,10 +21549,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G246" s="5" t="n">
+        <v>-0.152833</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -21931,10 +21873,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G251" s="5" t="n">
+        <v>0.23191</v>
       </c>
       <c r="H251" s="5" t="n">
         <v>-0.334074</v>
@@ -21995,10 +21935,8 @@
       <c r="F252" s="5" t="n">
         <v>-0.052816</v>
       </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G252" s="5" t="n">
+        <v>0.201213</v>
       </c>
       <c r="H252" s="5" t="n">
         <v>-0.06551800000000001</v>
@@ -22059,10 +21997,8 @@
       <c r="F253" s="5" t="n">
         <v>0.238488</v>
       </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G253" s="5" t="n">
+        <v>-0.256091</v>
       </c>
       <c r="H253" s="5" t="n">
         <v>0.006287</v>
@@ -22119,10 +22055,8 @@
       <c r="F254" s="5" t="n">
         <v>0.120391</v>
       </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G254" s="5" t="n">
+        <v>-0.396055</v>
       </c>
       <c r="H254" s="5" t="n">
         <v>0.098223</v>
@@ -22179,10 +22113,8 @@
       <c r="F255" s="5" t="n">
         <v>-0.380434</v>
       </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G255" s="5" t="n">
+        <v>0.334353</v>
       </c>
       <c r="H255" s="5" t="n">
         <v>-0.725397</v>
@@ -22241,10 +22173,8 @@
       <c r="F256" s="5" t="n">
         <v>0.052576</v>
       </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G256" s="5" t="n">
+        <v>-0.055625</v>
       </c>
       <c r="H256" s="5" t="n">
         <v>-0.007</v>
@@ -22309,10 +22239,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G257" s="5" t="n">
+        <v>-1.533785</v>
       </c>
       <c r="H257" s="5" t="n">
         <v>-1.968044</v>
@@ -22362,17 +22290,19 @@
           <t>Acquisition of investments</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E258" s="5" t="n">
         <v>-1.387733</v>
       </c>
       <c r="F258" s="5" t="n">
         <v>-1.724472</v>
       </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G258" s="5" t="n">
+        <v>-2.589785</v>
       </c>
       <c r="H258" s="5" t="n">
         <v>-2.413727</v>
@@ -22429,10 +22359,8 @@
       <c r="F259" s="5" t="n">
         <v>2.001205</v>
       </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G259" s="5" t="n">
+        <v>4.266749</v>
       </c>
       <c r="H259" s="5" t="n">
         <v>4.264971</v>
@@ -22489,10 +22417,8 @@
       <c r="F260" s="5" t="n">
         <v>-0.043239</v>
       </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G260" s="5" t="n">
+        <v>-0.352631</v>
       </c>
       <c r="H260" s="5" t="n">
         <v>-0.110248</v>
@@ -22551,10 +22477,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G261" s="5" t="n">
+        <v>0.219625</v>
       </c>
       <c r="H261" s="5" t="n">
         <v>0.38</v>
@@ -22743,10 +22667,8 @@
       <c r="F264" s="5" t="n">
         <v>0.325254</v>
       </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G264" s="5" t="n">
+        <v>1.543958</v>
       </c>
       <c r="H264" s="5" t="n">
         <v>2.120996</v>
@@ -23116,30 +23038,34 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Unrealized (gain) loss of investments</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
-      <c r="E270" s="5" t="n">
-        <v>-1.950089</v>
-      </c>
-      <c r="F270" s="5" t="n">
-        <v>-1.405829</v>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net income (loss) for the year $</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G270" s="5" t="n">
+        <v>5.28006</v>
+      </c>
+      <c r="H270" s="5" t="n">
+        <v>-5.622919</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
@@ -23185,25 +23111,25 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Income from property sale</t>
+          <t>(Gain) loss on settlement of debt</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
-      <c r="E271" s="5" t="n">
-        <v>-0.299381</v>
-      </c>
-      <c r="F271" s="5" t="n">
-        <v>-0.310313</v>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G271" s="5" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="H271" s="5" t="n">
+        <v>-0.05475</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
@@ -23249,29 +23175,25 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E272" s="5" t="n">
-        <v>0.024261</v>
-      </c>
-      <c r="F272" s="5" t="n">
-        <v>0.00292</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Unrealized loss (gain) on investment in private companies</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G272" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H272" s="5" t="n">
+        <v>-0.292413</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
@@ -23317,20 +23239,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Shares received for finder’s fees</t>
+          <t>Share received for services</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
-      <c r="E273" s="5" t="n">
-        <v>-0.0025</v>
-      </c>
-      <c r="F273" s="5" t="n">
-        <v>-0.029388</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G273" s="5" t="n">
+        <v>-0.042875</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -23381,10 +23305,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Gain on transaction</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>Deferred tax recovery</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -23395,10 +23323,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G274" s="5" t="n">
+        <v>-0.000425</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -23444,30 +23370,34 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Equity loss on affiliates</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
-      <c r="E275" s="5" t="n">
-        <v>0.096304</v>
-      </c>
-      <c r="F275" s="5" t="n">
-        <v>0.03375</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in cash during the year</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G275" s="5" t="n">
+        <v>0.010173</v>
+      </c>
+      <c r="H275" s="5" t="n">
+        <v>0.152952</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -23508,34 +23438,34 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Amounts receivable</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E276" s="5" t="n">
-        <v>-0.025798</v>
-      </c>
-      <c r="F276" s="5" t="n">
-        <v>-0.250306</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G276" s="5" t="n">
+        <v>0.124745</v>
+      </c>
+      <c r="H276" s="5" t="n">
+        <v>0.134918</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -23576,32 +23506,34 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Liability for flow-through shares</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>Cash, end of year $</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F277" s="5" t="n">
-        <v>0.008354</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G277" s="5" t="n">
+        <v>0.134918</v>
+      </c>
+      <c r="H277" s="5" t="n">
+        <v>0.28787</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -23642,24 +23574,20 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Cash (used in) operating activities</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Unrealized (gain) loss of investments</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" s="5" t="n">
-        <v>-1.508424</v>
+        <v>-1.950089</v>
       </c>
       <c r="F278" s="5" t="n">
-        <v>-0.856553</v>
+        <v>-1.405829</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -23710,20 +23638,20 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Loans receivable</t>
+          <t>Income from property sale</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
       <c r="E279" s="5" t="n">
-        <v>-0.105051</v>
+        <v>-0.299381</v>
       </c>
       <c r="F279" s="5" t="n">
-        <v>0.12551</v>
+        <v>-0.310313</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -23774,22 +23702,24 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Proceeds on sale of equity method investees</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E280" s="5" t="n">
-        <v>0.055735</v>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.024261</v>
+      </c>
+      <c r="F280" s="5" t="n">
+        <v>0.00292</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -23840,20 +23770,20 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Investment in equity method investees</t>
+          <t>Shares received for finder’s fees</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
       <c r="E281" s="5" t="n">
-        <v>-0.134301</v>
+        <v>-0.0025</v>
       </c>
       <c r="F281" s="5" t="n">
-        <v>-0.03375</v>
+        <v>-0.029388</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -23904,24 +23834,24 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares, net of share issuance costs</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E282" s="5" t="n">
-        <v>1.04921</v>
-      </c>
-      <c r="F282" s="5" t="n">
-        <v>0.469607</v>
+          <t>Gain on transaction</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
@@ -23972,24 +23902,20 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Cash provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Equity loss on affiliates</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
       <c r="E283" s="5" t="n">
-        <v>1.04921</v>
+        <v>0.096304</v>
       </c>
       <c r="F283" s="5" t="n">
-        <v>0.469607</v>
+        <v>0.03375</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
@@ -24035,29 +23961,29 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>REVENUES</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Administrative fees</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr"/>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amounts receivable</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E284" s="5" t="n">
+        <v>-0.025798</v>
+      </c>
+      <c r="F284" s="5" t="n">
+        <v>-0.250306</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
@@ -24084,30 +24010,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L284" s="5" t="n">
-        <v>0.961</v>
-      </c>
-      <c r="M284" s="5" t="n">
-        <v>1.584333</v>
-      </c>
-      <c r="N284" s="5" t="n">
-        <v>1.830729</v>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>REVENUES</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Corporate development and marketing</t>
+          <t>Liability for flow-through shares</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -24116,10 +24048,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F285" s="5" t="n">
+        <v>0.008354</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
@@ -24146,42 +24076,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L285" s="5" t="n">
-        <v>1.238859</v>
-      </c>
-      <c r="M285" s="5" t="n">
-        <v>1.142932</v>
-      </c>
-      <c r="N285" s="5" t="n">
-        <v>1.089822</v>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>REVENUES</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Gain (loss) from property sales 11</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr"/>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash (used in) operating activities</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E286" s="5" t="n">
+        <v>-1.508424</v>
+      </c>
+      <c r="F286" s="5" t="n">
+        <v>-0.856553</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -24213,43 +24149,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M286" s="5" t="n">
-        <v>-0.575</v>
-      </c>
-      <c r="N286" s="5" t="n">
-        <v>1.408839</v>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>REVENUES</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>REVENUES total</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loans receivable</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" s="5" t="n">
+        <v>-0.105051</v>
+      </c>
+      <c r="F287" s="5" t="n">
+        <v>0.12551</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
@@ -24276,41 +24208,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L287" s="5" t="n">
-        <v>2.545539</v>
-      </c>
-      <c r="M287" s="5" t="n">
-        <v>2.152265</v>
-      </c>
-      <c r="N287" s="5" t="n">
-        <v>4.32939</v>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>General and administrative expenses 15</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds on sale of equity method investees</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" s="5" t="n">
+        <v>0.055735</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24332,52 +24264,54 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J288" s="5" t="n">
-        <v>2.089636</v>
-      </c>
-      <c r="K288" s="5" t="n">
-        <v>3.388499</v>
-      </c>
-      <c r="L288" s="5" t="n">
-        <v>1.727767</v>
-      </c>
-      <c r="M288" s="5" t="n">
-        <v>2.2191</v>
-      </c>
-      <c r="N288" s="5" t="n">
-        <v>3.639619</v>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>INCOME (LOSS) BEFORE OTHER ITEMS</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Investment in equity method investees</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" s="5" t="n">
+        <v>-0.134301</v>
+      </c>
+      <c r="F289" s="5" t="n">
+        <v>-0.03375</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -24399,45 +24333,53 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K289" s="5" t="n">
-        <v>-1.708975</v>
-      </c>
-      <c r="L289" s="5" t="n">
-        <v>0.8177720000000001</v>
-      </c>
-      <c r="M289" s="5" t="n">
-        <v>-0.06683500000000001</v>
-      </c>
-      <c r="N289" s="5" t="n">
-        <v>0.689771</v>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Equity loss from investments in associates 7</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds from issuance of shares, net of share issuance costs</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E290" s="5" t="n">
+        <v>1.04921</v>
+      </c>
+      <c r="F290" s="5" t="n">
+        <v>0.469607</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
@@ -24469,39 +24411,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M290" s="5" t="n">
-        <v>-0.095711</v>
-      </c>
-      <c r="N290" s="5" t="n">
-        <v>-0.110267</v>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Fair market gain on investments in public companies 6</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E291" s="5" t="n">
+        <v>1.04921</v>
+      </c>
+      <c r="F291" s="5" t="n">
+        <v>0.469607</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
@@ -24533,11 +24479,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M291" s="5" t="n">
-        <v>5.213192</v>
-      </c>
-      <c r="N291" s="5" t="n">
-        <v>19.236646</v>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="292">
@@ -24548,12 +24498,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>REVENUES</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Fair market gain on promissory notes receivable</t>
+          <t>Administrative fees</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -24592,16 +24542,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L292" s="5" t="n">
+        <v>0.961</v>
       </c>
       <c r="M292" s="5" t="n">
-        <v>0.23584</v>
+        <v>1.584333</v>
       </c>
       <c r="N292" s="5" t="n">
-        <v>0.063024</v>
+        <v>1.830729</v>
       </c>
     </row>
     <row r="293">
@@ -24612,12 +24560,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>REVENUES</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Fair market value adjustment on investment in associates 7</t>
+          <t>Corporate development and marketing</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -24656,16 +24604,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L293" s="5" t="n">
+        <v>1.238859</v>
       </c>
       <c r="M293" s="5" t="n">
-        <v>-0.020679</v>
+        <v>1.142932</v>
       </c>
       <c r="N293" s="5" t="n">
-        <v>-0.073452</v>
+        <v>1.089822</v>
       </c>
     </row>
     <row r="294">
@@ -24676,12 +24622,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>REVENUES</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Gain on sale of investments 6,7</t>
+          <t>Gain (loss) from property sales 11</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -24726,10 +24672,10 @@
         </is>
       </c>
       <c r="M294" s="5" t="n">
-        <v>0.236064</v>
+        <v>-0.575</v>
       </c>
       <c r="N294" s="5" t="n">
-        <v>0.136601</v>
+        <v>1.408839</v>
       </c>
     </row>
     <row r="295">
@@ -24740,15 +24686,19 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>REVENUES</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Impairment of mineral properties 11</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
+          <t>REVENUES total</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -24774,20 +24724,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J295" s="5" t="n">
-        <v>-0.003985</v>
-      </c>
-      <c r="K295" s="5" t="n">
-        <v>-0.003712</v>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L295" s="5" t="n">
-        <v>-0.06865599999999999</v>
+        <v>2.545539</v>
       </c>
       <c r="M295" s="5" t="n">
-        <v>-0.095693</v>
+        <v>2.152265</v>
       </c>
       <c r="N295" s="5" t="n">
-        <v>-0.0095</v>
+        <v>4.32939</v>
       </c>
     </row>
     <row r="296">
@@ -24798,17 +24752,17 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>General and administrative expenses 15</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -24837,19 +24791,19 @@
         </is>
       </c>
       <c r="J296" s="5" t="n">
-        <v>0.000159</v>
+        <v>2.089636</v>
       </c>
       <c r="K296" s="5" t="n">
-        <v>0.001249</v>
+        <v>3.388499</v>
       </c>
       <c r="L296" s="5" t="n">
-        <v>0.001494</v>
+        <v>1.727767</v>
       </c>
       <c r="M296" s="5" t="n">
-        <v>0.001787</v>
+        <v>2.2191</v>
       </c>
       <c r="N296" s="5" t="n">
-        <v>0.001837</v>
+        <v>3.639619</v>
       </c>
     </row>
     <row r="297">
@@ -24860,15 +24814,19 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Gain on derecognition of equity investee 7</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>INCOME (LOSS) BEFORE OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -24899,23 +24857,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K297" s="5" t="n">
+        <v>-1.708975</v>
+      </c>
+      <c r="L297" s="5" t="n">
+        <v>0.8177720000000001</v>
       </c>
       <c r="M297" s="5" t="n">
-        <v>0.364449</v>
-      </c>
-      <c r="N297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.06683500000000001</v>
+      </c>
+      <c r="N297" s="5" t="n">
+        <v>0.689771</v>
       </c>
     </row>
     <row r="298">
@@ -24931,7 +24883,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>(Loss) gain on settlement of debt</t>
+          <t>Equity loss from investments in associates 7</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -24976,10 +24928,10 @@
         </is>
       </c>
       <c r="M298" s="5" t="n">
-        <v>0.109375</v>
+        <v>-0.095711</v>
       </c>
       <c r="N298" s="5" t="n">
-        <v>-0.0105</v>
+        <v>-0.110267</v>
       </c>
     </row>
     <row r="299">
@@ -24995,14 +24947,10 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Fair market gain on investments in public companies 6</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -25033,17 +24981,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K299" s="5" t="n">
-        <v>0.034166</v>
-      </c>
-      <c r="L299" s="5" t="n">
-        <v>0.033782</v>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M299" s="5" t="n">
-        <v>0.0143</v>
+        <v>5.213192</v>
       </c>
       <c r="N299" s="5" t="n">
-        <v>0.10125</v>
+        <v>19.236646</v>
       </c>
     </row>
     <row r="300">
@@ -25059,7 +25011,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>OTHER ITEMS total</t>
+          <t>Fair market gain on promissory notes receivable</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -25088,20 +25040,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J300" s="5" t="n">
-        <v>10.152017</v>
-      </c>
-      <c r="K300" s="5" t="n">
-        <v>-8.820771000000001</v>
-      </c>
-      <c r="L300" s="5" t="n">
-        <v>-4.478015</v>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M300" s="5" t="n">
-        <v>5.962924</v>
+        <v>0.23584</v>
       </c>
       <c r="N300" s="5" t="n">
-        <v>19.335639</v>
+        <v>0.063024</v>
       </c>
     </row>
     <row r="301">
@@ -25117,14 +25075,10 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>INCOME BEFORE INCOME TAXES</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Fair market value adjustment on investment in associates 7</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -25166,10 +25120,10 @@
         </is>
       </c>
       <c r="M301" s="5" t="n">
-        <v>5.896089</v>
+        <v>-0.020679</v>
       </c>
       <c r="N301" s="5" t="n">
-        <v>20.02541</v>
+        <v>-0.073452</v>
       </c>
     </row>
     <row r="302">
@@ -25180,19 +25134,15 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>INCOME TAXES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Deferred income tax expense</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Gain on sale of investments 6,7</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -25233,13 +25183,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M302" s="5" t="n">
+        <v>0.236064</v>
       </c>
       <c r="N302" s="5" t="n">
-        <v>0.745345</v>
+        <v>0.136601</v>
       </c>
     </row>
     <row r="303">
@@ -25250,19 +25198,15 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>INCOME TAXES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>NET INCOME AND COMPREHENSIVE INCOME FOR THE YEAR</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Impairment of mineral properties 11</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -25288,26 +25232,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J303" s="5" t="n">
+        <v>-0.003985</v>
+      </c>
+      <c r="K303" s="5" t="n">
+        <v>-0.003712</v>
+      </c>
+      <c r="L303" s="5" t="n">
+        <v>-0.06865599999999999</v>
       </c>
       <c r="M303" s="5" t="n">
-        <v>5.896089</v>
+        <v>-0.095693</v>
       </c>
       <c r="N303" s="5" t="n">
-        <v>19.280065</v>
+        <v>-0.0095</v>
       </c>
     </row>
     <row r="304">
@@ -25318,17 +25256,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>INCOME TAXES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Basic earnings per share</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -25356,26 +25294,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J304" s="5" t="n">
+        <v>0.000159</v>
+      </c>
+      <c r="K304" s="5" t="n">
+        <v>0.001249</v>
+      </c>
+      <c r="L304" s="5" t="n">
+        <v>0.001494</v>
       </c>
       <c r="M304" s="5" t="n">
-        <v>4.6e-07</v>
+        <v>0.001787</v>
       </c>
       <c r="N304" s="5" t="n">
-        <v>1.52e-06</v>
+        <v>0.001837</v>
       </c>
     </row>
     <row r="305">
@@ -25386,19 +25318,15 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>INCOME TAXES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Diluted earnings per share</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Gain on derecognition of equity investee 7</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -25440,10 +25368,12 @@
         </is>
       </c>
       <c r="M305" s="5" t="n">
-        <v>3.1e-07</v>
-      </c>
-      <c r="N305" s="5" t="n">
-        <v>1.43e-06</v>
+        <v>0.364449</v>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="306">
@@ -25454,19 +25384,15 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>(Loss) gain on settlement of debt</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -25492,20 +25418,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J306" s="5" t="n">
-        <v>16.106483</v>
-      </c>
-      <c r="K306" s="5" t="n">
-        <v>24.104949</v>
-      </c>
-      <c r="L306" s="5" t="n">
-        <v>47.967139</v>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M306" s="5" t="n">
-        <v>12.68263</v>
+        <v>0.109375</v>
       </c>
       <c r="N306" s="5" t="n">
-        <v>12.706519</v>
+        <v>-0.0105</v>
       </c>
     </row>
     <row r="307">
@@ -25516,17 +25448,17 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Diluted</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>DilutedAverageShares</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -25554,20 +25486,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J307" s="5" t="n">
-        <v>16.17121</v>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K307" s="5" t="n">
-        <v>24.104949</v>
+        <v>0.034166</v>
       </c>
       <c r="L307" s="5" t="n">
-        <v>47.967139</v>
+        <v>0.033782</v>
       </c>
       <c r="M307" s="5" t="n">
-        <v>19.249329</v>
+        <v>0.0143</v>
       </c>
       <c r="N307" s="5" t="n">
-        <v>13.461016</v>
+        <v>0.10125</v>
       </c>
     </row>
     <row r="308">
@@ -25578,12 +25512,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>REVENUES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>(Loss) income from property sales 11</t>
+          <t>OTHER ITEMS total</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -25612,26 +25546,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J308" s="5" t="n">
+        <v>10.152017</v>
+      </c>
+      <c r="K308" s="5" t="n">
+        <v>-8.820771000000001</v>
       </c>
       <c r="L308" s="5" t="n">
-        <v>0.34568</v>
+        <v>-4.478015</v>
       </c>
       <c r="M308" s="5" t="n">
-        <v>-0.575</v>
-      </c>
-      <c r="N308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.962924</v>
+      </c>
+      <c r="N308" s="5" t="n">
+        <v>19.335639</v>
       </c>
     </row>
     <row r="309">
@@ -25642,15 +25570,19 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>(LOSS) INCOME BEFORE OTHER ITEMS</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
+          <t>INCOME BEFORE INCOME TAXES</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -25676,22 +25608,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J309" s="5" t="n">
-        <v>0.14019</v>
-      </c>
-      <c r="K309" s="5" t="n">
-        <v>-1.708975</v>
-      </c>
-      <c r="L309" s="5" t="n">
-        <v>0.8177720000000001</v>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M309" s="5" t="n">
-        <v>-0.06683500000000001</v>
-      </c>
-      <c r="N309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.896089</v>
+      </c>
+      <c r="N309" s="5" t="n">
+        <v>20.02541</v>
       </c>
     </row>
     <row r="310">
@@ -25702,15 +25638,19 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>INCOME TAXES</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Equity loss from investment in associates 7</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>Deferred income tax expense</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -25741,19 +25681,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K310" s="5" t="n">
-        <v>-0.134464</v>
-      </c>
-      <c r="L310" s="5" t="n">
-        <v>-0.292669</v>
-      </c>
-      <c r="M310" s="5" t="n">
-        <v>-0.095711</v>
-      </c>
-      <c r="N310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N310" s="5" t="n">
+        <v>0.745345</v>
       </c>
     </row>
     <row r="311">
@@ -25764,15 +25708,19 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>INCOME TAXES</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Fair market gain (loss) on investments in public companies 6</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>NET INCOME AND COMPREHENSIVE INCOME FOR THE YEAR</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -25808,16 +25756,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L311" s="5" t="n">
-        <v>-2.22556</v>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M311" s="5" t="n">
-        <v>5.213192</v>
-      </c>
-      <c r="N311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.896089</v>
+      </c>
+      <c r="N311" s="5" t="n">
+        <v>19.280065</v>
       </c>
     </row>
     <row r="312">
@@ -25828,15 +25776,19 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>INCOME TAXES</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Fair market gain (loss) on promissory notes receivable</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>Basic earnings per share</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -25872,16 +25824,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L312" s="5" t="n">
-        <v>-0.07525</v>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M312" s="5" t="n">
-        <v>0.23584</v>
-      </c>
-      <c r="N312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.6e-07</v>
+      </c>
+      <c r="N312" s="5" t="n">
+        <v>1.52e-06</v>
       </c>
     </row>
     <row r="313">
@@ -25892,15 +25844,19 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>INCOME TAXES</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Impairment loss on investment in associates 7</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>Diluted earnings per share</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -25936,16 +25892,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L313" s="5" t="n">
-        <v>-1.088296</v>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M313" s="5" t="n">
-        <v>-0.020679</v>
-      </c>
-      <c r="N313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.1e-07</v>
+      </c>
+      <c r="N313" s="5" t="n">
+        <v>1.43e-06</v>
       </c>
     </row>
     <row r="314">
@@ -25956,15 +25912,19 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Gain (loss) on sale of investments 6,7</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -25990,26 +25950,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J314" s="5" t="n">
+        <v>16.106483</v>
+      </c>
+      <c r="K314" s="5" t="n">
+        <v>24.104949</v>
       </c>
       <c r="L314" s="5" t="n">
-        <v>-0.660334</v>
+        <v>47.967139</v>
       </c>
       <c r="M314" s="5" t="n">
-        <v>0.236064</v>
-      </c>
-      <c r="N314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>12.68263</v>
+      </c>
+      <c r="N314" s="5" t="n">
+        <v>12.706519</v>
       </c>
     </row>
     <row r="315">
@@ -26020,15 +25974,19 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>WEIGHTED AVERAGE NUMBER OF SHARES OUTSTANDING</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Gain on settlement of debt</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>Diluted</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -26054,28 +26012,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J315" s="5" t="n">
+        <v>16.17121</v>
+      </c>
+      <c r="K315" s="5" t="n">
+        <v>24.104949</v>
+      </c>
+      <c r="L315" s="5" t="n">
+        <v>47.967139</v>
       </c>
       <c r="M315" s="5" t="n">
-        <v>0.109375</v>
-      </c>
-      <c r="N315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>19.249329</v>
+      </c>
+      <c r="N315" s="5" t="n">
+        <v>13.461016</v>
       </c>
     </row>
     <row r="316">
@@ -26086,12 +26036,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>REVENUES</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Write off marketable securities 6</t>
+          <t>(Loss) income from property sales 11</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -26131,12 +26081,10 @@
         </is>
       </c>
       <c r="L316" s="5" t="n">
-        <v>-0.055026</v>
-      </c>
-      <c r="M316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.34568</v>
+      </c>
+      <c r="M316" s="5" t="n">
+        <v>-0.575</v>
       </c>
       <c r="N316" t="inlineStr">
         <is>
@@ -26152,12 +26100,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Write off promissory notes receivable 8</t>
+          <t>(LOSS) INCOME BEFORE OTHER ITEMS</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -26186,23 +26134,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J317" s="5" t="n">
+        <v>0.14019</v>
+      </c>
+      <c r="K317" s="5" t="n">
+        <v>-1.708975</v>
       </c>
       <c r="L317" s="5" t="n">
-        <v>-0.0475</v>
-      </c>
-      <c r="M317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.8177720000000001</v>
+      </c>
+      <c r="M317" s="5" t="n">
+        <v>-0.06683500000000001</v>
       </c>
       <c r="N317" t="inlineStr">
         <is>
@@ -26218,12 +26160,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>NET INCOME (LOSS) AND COMPREHENSIVE INCOME (LOSS)</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>FOR THE YEAR</t>
+          <t>Equity loss from investment in associates 7</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -26257,16 +26199,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K318" s="5" t="n">
+        <v>-0.134464</v>
       </c>
       <c r="L318" s="5" t="n">
-        <v>-3.660243</v>
+        <v>-0.292669</v>
       </c>
       <c r="M318" s="5" t="n">
-        <v>5.896089</v>
+        <v>-0.095711</v>
       </c>
       <c r="N318" t="inlineStr">
         <is>
@@ -26282,19 +26222,15 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>NET INCOME (LOSS) AND COMPREHENSIVE INCOME (LOSS)</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Basic earnings (loss) per share</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Fair market gain (loss) on investments in public companies 6</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -26331,10 +26267,10 @@
         </is>
       </c>
       <c r="L319" s="5" t="n">
-        <v>-8e-08</v>
+        <v>-2.22556</v>
       </c>
       <c r="M319" s="5" t="n">
-        <v>9e-08</v>
+        <v>5.213192</v>
       </c>
       <c r="N319" t="inlineStr">
         <is>
@@ -26350,19 +26286,15 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>NET INCOME (LOSS) AND COMPREHENSIVE INCOME (LOSS)</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Diluted earnings (loss) per share</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Fair market gain (loss) on promissory notes receivable</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -26399,10 +26331,10 @@
         </is>
       </c>
       <c r="L320" s="5" t="n">
-        <v>-8e-08</v>
+        <v>-0.07525</v>
       </c>
       <c r="M320" s="5" t="n">
-        <v>5.999999999999999e-08</v>
+        <v>0.23584</v>
       </c>
       <c r="N320" t="inlineStr">
         <is>
@@ -26418,12 +26350,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Administrative fees</t>
+          <t>Impairment loss on investment in associates 7</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -26452,19 +26384,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J321" s="5" t="n">
-        <v>0.794092</v>
-      </c>
-      <c r="K321" s="5" t="n">
-        <v>0.806472</v>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L321" s="5" t="n">
-        <v>0.961</v>
-      </c>
-      <c r="M321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.088296</v>
+      </c>
+      <c r="M321" s="5" t="n">
+        <v>-0.020679</v>
       </c>
       <c r="N321" t="inlineStr">
         <is>
@@ -26480,12 +26414,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Corporate development and marketing</t>
+          <t>Gain (loss) on sale of investments 6,7</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -26514,19 +26448,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J322" s="5" t="n">
-        <v>1.15085</v>
-      </c>
-      <c r="K322" s="5" t="n">
-        <v>0.886452</v>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L322" s="5" t="n">
-        <v>1.238859</v>
-      </c>
-      <c r="M322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.660334</v>
+      </c>
+      <c r="M322" s="5" t="n">
+        <v>0.236064</v>
       </c>
       <c r="N322" t="inlineStr">
         <is>
@@ -26542,12 +26478,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Income (loss) from property sales 11</t>
+          <t>Gain on settlement of debt</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -26581,16 +26517,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K323" s="5" t="n">
-        <v>-0.0134</v>
-      </c>
-      <c r="L323" s="5" t="n">
-        <v>0.34568</v>
-      </c>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M323" s="5" t="n">
+        <v>0.109375</v>
       </c>
       <c r="N323" t="inlineStr">
         <is>
@@ -26606,19 +26544,15 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>REVENUE total</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Write off marketable securities 6</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -26644,14 +26578,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J324" s="5" t="n">
-        <v>2.229826</v>
-      </c>
-      <c r="K324" s="5" t="n">
-        <v>1.679524</v>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L324" s="5" t="n">
-        <v>2.545539</v>
+        <v>-0.055026</v>
       </c>
       <c r="M324" t="inlineStr">
         <is>
@@ -26677,7 +26615,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Fair market loss on investments in public companies 6</t>
+          <t>Write off promissory notes receivable 8</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -26711,11 +26649,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K325" s="5" t="n">
-        <v>-9.428834</v>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L325" s="5" t="n">
-        <v>-2.22556</v>
+        <v>-0.0475</v>
       </c>
       <c r="M325" t="inlineStr">
         <is>
@@ -26736,12 +26676,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>NET INCOME (LOSS) AND COMPREHENSIVE INCOME (LOSS)</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Fair market loss on investment in private companies 6</t>
+          <t>FOR THE YEAR</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
@@ -26775,18 +26715,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K326" s="5" t="n">
-        <v>-0.062374</v>
-      </c>
-      <c r="L326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L326" s="5" t="n">
+        <v>-3.660243</v>
+      </c>
+      <c r="M326" s="5" t="n">
+        <v>5.896089</v>
       </c>
       <c r="N326" t="inlineStr">
         <is>
@@ -26802,15 +26740,19 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>NET INCOME (LOSS) AND COMPREHENSIVE INCOME (LOSS)</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Fair market loss on promissory notes receivable</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr"/>
+          <t>Basic earnings (loss) per share</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -26841,16 +26783,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K327" s="5" t="n">
-        <v>-0.188125</v>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L327" s="5" t="n">
-        <v>-0.07525</v>
-      </c>
-      <c r="M327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8e-08</v>
+      </c>
+      <c r="M327" s="5" t="n">
+        <v>9e-08</v>
       </c>
       <c r="N327" t="inlineStr">
         <is>
@@ -26866,15 +26808,19 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>NET INCOME (LOSS) AND COMPREHENSIVE INCOME (LOSS)</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>(Loss) gain on sale of investments 6,7</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>Diluted earnings (loss) per share</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -26905,16 +26851,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K328" s="5" t="n">
-        <v>0.932183</v>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L328" s="5" t="n">
-        <v>-0.660334</v>
-      </c>
-      <c r="M328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8e-08</v>
+      </c>
+      <c r="M328" s="5" t="n">
+        <v>5.999999999999999e-08</v>
       </c>
       <c r="N328" t="inlineStr">
         <is>
@@ -26930,12 +26876,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Gain on sale of debt</t>
+          <t>Administrative fees</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
@@ -26964,18 +26910,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J329" s="5" t="n">
+        <v>0.794092</v>
       </c>
       <c r="K329" s="5" t="n">
-        <v>0.02914</v>
-      </c>
-      <c r="L329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.806472</v>
+      </c>
+      <c r="L329" s="5" t="n">
+        <v>0.961</v>
       </c>
       <c r="M329" t="inlineStr">
         <is>
@@ -26996,19 +26938,15 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>LOSS BEFORE INCOME TAX</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Corporate development and marketing</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -27034,16 +26972,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J330" s="5" t="n">
+        <v>1.15085</v>
       </c>
       <c r="K330" s="5" t="n">
-        <v>-10.529746</v>
+        <v>0.886452</v>
       </c>
       <c r="L330" s="5" t="n">
-        <v>-3.660243</v>
+        <v>1.238859</v>
       </c>
       <c r="M330" t="inlineStr">
         <is>
@@ -27064,12 +27000,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Deferred tax recovery 20</t>
+          <t>Income (loss) from property sales 11</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
@@ -27104,12 +27040,10 @@
         </is>
       </c>
       <c r="K331" s="5" t="n">
-        <v>0.055127</v>
-      </c>
-      <c r="L331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.0134</v>
+      </c>
+      <c r="L331" s="5" t="n">
+        <v>0.34568</v>
       </c>
       <c r="M331" t="inlineStr">
         <is>
@@ -27130,17 +27064,17 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>NET LOSS AND COMPREHENSIVE LOSS FOR THE YEAR</t>
+          <t>REVENUE total</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -27168,16 +27102,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J332" s="5" t="n">
+        <v>2.229826</v>
       </c>
       <c r="K332" s="5" t="n">
-        <v>-10.474619</v>
+        <v>1.679524</v>
       </c>
       <c r="L332" s="5" t="n">
-        <v>-3.660243</v>
+        <v>2.545539</v>
       </c>
       <c r="M332" t="inlineStr">
         <is>
@@ -27203,7 +27135,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Basic loss per share</t>
+          <t>Fair market loss on investments in public companies 6</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
@@ -27238,10 +27170,10 @@
         </is>
       </c>
       <c r="K333" s="5" t="n">
-        <v>-4.3e-07</v>
+        <v>-9.428834</v>
       </c>
       <c r="L333" s="5" t="n">
-        <v>-8e-08</v>
+        <v>-2.22556</v>
       </c>
       <c r="M333" t="inlineStr">
         <is>
@@ -27267,7 +27199,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Diluted loss per share</t>
+          <t>Fair market loss on investment in private companies 6</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
@@ -27302,10 +27234,12 @@
         </is>
       </c>
       <c r="K334" s="5" t="n">
-        <v>-4.3e-07</v>
-      </c>
-      <c r="L334" s="5" t="n">
-        <v>-8e-08</v>
+        <v>-0.062374</v>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
@@ -27326,12 +27260,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>(Loss) income from property sales 11</t>
+          <t>Fair market loss on promissory notes receivable</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -27360,16 +27294,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J335" s="5" t="n">
-        <v>0.284884</v>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K335" s="5" t="n">
-        <v>-0.0134</v>
-      </c>
-      <c r="L335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.188125</v>
+      </c>
+      <c r="L335" s="5" t="n">
+        <v>-0.07525</v>
       </c>
       <c r="M335" t="inlineStr">
         <is>
@@ -27395,7 +27329,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Equity (loss) recovery from investment in associates 7</t>
+          <t>(Loss) gain on sale of investments 6,7</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -27424,16 +27358,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J336" s="5" t="n">
-        <v>0.127034</v>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K336" s="5" t="n">
-        <v>-0.134464</v>
-      </c>
-      <c r="L336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.932183</v>
+      </c>
+      <c r="L336" s="5" t="n">
+        <v>-0.660334</v>
       </c>
       <c r="M336" t="inlineStr">
         <is>
@@ -27459,7 +27393,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Fair market value gain on investment in associate</t>
+          <t>Gain on sale of debt</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
@@ -27488,13 +27422,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J337" s="5" t="n">
-        <v>1.18133</v>
-      </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K337" s="5" t="n">
+        <v>0.02914</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -27525,10 +27459,14 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Fair market (loss) gain on investments in public companies 6</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>LOSS BEFORE INCOME TAX</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -27554,16 +27492,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J338" s="5" t="n">
-        <v>6.090243</v>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K338" s="5" t="n">
-        <v>-9.428834</v>
-      </c>
-      <c r="L338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-10.529746</v>
+      </c>
+      <c r="L338" s="5" t="n">
+        <v>-3.660243</v>
       </c>
       <c r="M338" t="inlineStr">
         <is>
@@ -27589,7 +27527,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Fair market gain on investment in private companies 6</t>
+          <t>Deferred tax recovery 20</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
@@ -27618,11 +27556,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J339" s="5" t="n">
-        <v>0.581361</v>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K339" s="5" t="n">
-        <v>-0.062374</v>
+        <v>0.055127</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -27653,10 +27593,14 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Fair market (loss) on promissory notes receivable</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr"/>
+          <t>NET LOSS AND COMPREHENSIVE LOSS FOR THE YEAR</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -27688,12 +27632,10 @@
         </is>
       </c>
       <c r="K340" s="5" t="n">
-        <v>-0.188125</v>
-      </c>
-      <c r="L340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-10.474619</v>
+      </c>
+      <c r="L340" s="5" t="n">
+        <v>-3.660243</v>
       </c>
       <c r="M340" t="inlineStr">
         <is>
@@ -27719,7 +27661,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Gain on derecognition on investment in associate</t>
+          <t>Basic loss per share</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -27748,18 +27690,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J341" s="5" t="n">
-        <v>0.857593</v>
-      </c>
-      <c r="K341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K341" s="5" t="n">
+        <v>-4.3e-07</v>
+      </c>
+      <c r="L341" s="5" t="n">
+        <v>-8e-08</v>
       </c>
       <c r="M341" t="inlineStr">
         <is>
@@ -27785,7 +27725,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Gain on sale of investment</t>
+          <t>Diluted loss per share</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -27814,16 +27754,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J342" s="5" t="n">
-        <v>1.270656</v>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K342" s="5" t="n">
-        <v>0.932183</v>
-      </c>
-      <c r="L342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.3e-07</v>
+      </c>
+      <c r="L342" s="5" t="n">
+        <v>-8e-08</v>
       </c>
       <c r="M342" t="inlineStr">
         <is>
@@ -27844,12 +27784,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Gain on government loan 17</t>
+          <t>(Loss) income from property sales 11</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
@@ -27879,12 +27819,10 @@
         </is>
       </c>
       <c r="J343" s="5" t="n">
-        <v>0.012626</v>
-      </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.284884</v>
+      </c>
+      <c r="K343" s="5" t="n">
+        <v>-0.0134</v>
       </c>
       <c r="L343" t="inlineStr">
         <is>
@@ -27915,7 +27853,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Other (expense) income</t>
+          <t>Equity (loss) recovery from investment in associates 7</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
@@ -27945,10 +27883,10 @@
         </is>
       </c>
       <c r="J344" s="5" t="n">
-        <v>-0.015</v>
+        <v>0.127034</v>
       </c>
       <c r="K344" s="5" t="n">
-        <v>0.034166</v>
+        <v>-0.134464</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -27979,7 +27917,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Recovery of marketable securities written off 7</t>
+          <t>Fair market value gain on investment in associate</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
@@ -28009,7 +27947,7 @@
         </is>
       </c>
       <c r="J345" s="5" t="n">
-        <v>0.05</v>
+        <v>1.18133</v>
       </c>
       <c r="K345" t="inlineStr">
         <is>
@@ -28045,7 +27983,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>(LOSS) INCOME BEFORE INCOME TAX</t>
+          <t>Fair market (loss) gain on investments in public companies 6</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
@@ -28075,10 +28013,10 @@
         </is>
       </c>
       <c r="J346" s="5" t="n">
-        <v>10.292207</v>
+        <v>6.090243</v>
       </c>
       <c r="K346" s="5" t="n">
-        <v>-10.529746</v>
+        <v>-9.428834</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
@@ -28109,7 +28047,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Deferred tax recovery (expense) 20</t>
+          <t>Fair market gain on investment in private companies 6</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
@@ -28139,10 +28077,10 @@
         </is>
       </c>
       <c r="J347" s="5" t="n">
-        <v>-0.055127</v>
+        <v>0.581361</v>
       </c>
       <c r="K347" s="5" t="n">
-        <v>0.055127</v>
+        <v>-0.062374</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -28168,12 +28106,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>NET (LOSS) INCOME AND COMPREHENSIVE (LOSS) INCOME</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>FOR THE YEAR</t>
+          <t>Fair market (loss) on promissory notes receivable</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
@@ -28202,11 +28140,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J348" s="5" t="n">
-        <v>10.23708</v>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K348" s="5" t="n">
-        <v>-10.474619</v>
+        <v>-0.188125</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -28232,19 +28172,15 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>NET (LOSS) INCOME AND COMPREHENSIVE (LOSS) INCOME</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Basic income (loss) per share</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Gain on derecognition on investment in associate</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -28271,10 +28207,12 @@
         </is>
       </c>
       <c r="J349" s="5" t="n">
-        <v>6.4e-07</v>
-      </c>
-      <c r="K349" s="5" t="n">
-        <v>-4.3e-07</v>
+        <v>0.857593</v>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
@@ -28300,19 +28238,15 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>NET (LOSS) INCOME AND COMPREHENSIVE (LOSS) INCOME</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Diluted income (loss) per share</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Gain on sale of investment</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -28339,10 +28273,10 @@
         </is>
       </c>
       <c r="J350" s="5" t="n">
-        <v>6.3e-07</v>
+        <v>1.270656</v>
       </c>
       <c r="K350" s="5" t="n">
-        <v>-4.3e-07</v>
+        <v>0.932183</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -28368,36 +28302,42 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Administrative fees $</t>
+          <t>Gain on government loan 17</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
-      <c r="E351" s="5" t="n">
-        <v>1.276312</v>
-      </c>
-      <c r="F351" s="5" t="n">
-        <v>1.41572</v>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H351" s="5" t="n">
-        <v>0.7225</v>
-      </c>
-      <c r="I351" s="5" t="n">
-        <v>0.6215000000000001</v>
-      </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J351" s="5" t="n">
+        <v>0.012626</v>
       </c>
       <c r="K351" t="inlineStr">
         <is>
@@ -28428,41 +28368,45 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Corporate development and marketing</t>
+          <t>Other (expense) income</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
-      <c r="E352" s="5" t="n">
-        <v>0.320889</v>
-      </c>
-      <c r="F352" s="5" t="n">
-        <v>0.557924</v>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H352" s="5" t="n">
-        <v>1.202112</v>
-      </c>
-      <c r="I352" s="5" t="n">
-        <v>0.746167</v>
-      </c>
-      <c r="J352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J352" s="5" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="K352" s="5" t="n">
+        <v>0.034166</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -28488,12 +28432,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Income from property sales (Note 12)</t>
+          <t>Recovery of marketable securities written off 7</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -28512,16 +28456,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H353" s="5" t="n">
-        <v>0.5436260000000001</v>
-      </c>
-      <c r="I353" s="5" t="n">
-        <v>0.1196</v>
-      </c>
-      <c r="J353" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J353" s="5" t="n">
+        <v>0.05</v>
       </c>
       <c r="K353" t="inlineStr">
         <is>
@@ -28552,45 +28498,45 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Revenue total</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E354" s="5" t="n">
-        <v>0.262134</v>
-      </c>
-      <c r="F354" s="5" t="n">
-        <v>0.328319</v>
+          <t>(LOSS) INCOME BEFORE INCOME TAX</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H354" s="5" t="n">
-        <v>2.468238</v>
-      </c>
-      <c r="I354" s="5" t="n">
-        <v>1.487267</v>
-      </c>
-      <c r="J354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J354" s="5" t="n">
+        <v>10.292207</v>
+      </c>
+      <c r="K354" s="5" t="n">
+        <v>-10.529746</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -28616,19 +28562,15 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>General and administrative expenses (Note 16)</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Deferred tax recovery (expense) 20</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -28644,21 +28586,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H355" s="5" t="n">
-        <v>2.835272</v>
-      </c>
-      <c r="I355" s="5" t="n">
-        <v>2.491108</v>
-      </c>
-      <c r="J355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J355" s="5" t="n">
+        <v>-0.055127</v>
+      </c>
+      <c r="K355" s="5" t="n">
+        <v>0.055127</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -28684,45 +28626,45 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>NET (LOSS) INCOME AND COMPREHENSIVE (LOSS) INCOME</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E356" s="5" t="n">
-        <v>-2.858595</v>
-      </c>
-      <c r="F356" s="5" t="n">
-        <v>-2.282645</v>
+          <t>FOR THE YEAR</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H356" s="5" t="n">
-        <v>-0.367034</v>
-      </c>
-      <c r="I356" s="5" t="n">
-        <v>-1.003841</v>
-      </c>
-      <c r="J356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J356" s="5" t="n">
+        <v>10.23708</v>
+      </c>
+      <c r="K356" s="5" t="n">
+        <v>-10.474619</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -28748,15 +28690,19 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>NET (LOSS) INCOME AND COMPREHENSIVE (LOSS) INCOME</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Equity loss from investment in associates (Note 7)</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>Basic income (loss) per share</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -28772,21 +28718,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H357" s="5" t="n">
-        <v>-0.026008</v>
-      </c>
-      <c r="I357" s="5" t="n">
-        <v>-0.156582</v>
-      </c>
-      <c r="J357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J357" s="5" t="n">
+        <v>6.4e-07</v>
+      </c>
+      <c r="K357" s="5" t="n">
+        <v>-4.3e-07</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -28812,17 +28758,17 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>NET (LOSS) INCOME AND COMPREHENSIVE (LOSS) INCOME</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
+          <t>Diluted income (loss) per share</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>DilutedEPS</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -28840,23 +28786,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H358" s="5" t="n">
-        <v>5e-06</v>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J358" s="5" t="n">
+        <v>6.3e-07</v>
+      </c>
+      <c r="K358" s="5" t="n">
+        <v>-4.3e-07</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
@@ -28882,20 +28826,20 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Gain on purchase of debt</t>
+          <t>Administrative fees $</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
       <c r="E359" s="5" t="n">
-        <v>0.46623</v>
+        <v>1.276312</v>
       </c>
       <c r="F359" s="5" t="n">
-        <v>0.733331</v>
+        <v>1.41572</v>
       </c>
       <c r="G359" t="inlineStr">
         <is>
@@ -28903,12 +28847,10 @@
         </is>
       </c>
       <c r="H359" s="5" t="n">
-        <v>0.000648</v>
-      </c>
-      <c r="I359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.7225</v>
+      </c>
+      <c r="I359" s="5" t="n">
+        <v>0.6215000000000001</v>
       </c>
       <c r="J359" t="inlineStr">
         <is>
@@ -28944,24 +28886,20 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Gain on settlement of debt (Note 20)</t>
+          <t>Corporate development and marketing</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E360" s="5" t="n">
+        <v>0.320889</v>
+      </c>
+      <c r="F360" s="5" t="n">
+        <v>0.557924</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -28969,12 +28907,10 @@
         </is>
       </c>
       <c r="H360" s="5" t="n">
-        <v>0.05475</v>
-      </c>
-      <c r="I360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.202112</v>
+      </c>
+      <c r="I360" s="5" t="n">
+        <v>0.746167</v>
       </c>
       <c r="J360" t="inlineStr">
         <is>
@@ -29010,12 +28946,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Income from sale of software (Note 21)</t>
+          <t>Income from property sales (Note 12)</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
@@ -29035,12 +28971,10 @@
         </is>
       </c>
       <c r="H361" s="5" t="n">
-        <v>0.135321</v>
-      </c>
-      <c r="I361" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.5436260000000001</v>
+      </c>
+      <c r="I361" s="5" t="n">
+        <v>0.1196</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -29076,24 +29010,24 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Impairment of mineral properties (Note 12)</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr"/>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Revenue total</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E362" s="5" t="n">
+        <v>0.262134</v>
+      </c>
+      <c r="F362" s="5" t="n">
+        <v>0.328319</v>
       </c>
       <c r="G362" t="inlineStr">
         <is>
@@ -29101,10 +29035,10 @@
         </is>
       </c>
       <c r="H362" s="5" t="n">
-        <v>-0.134665</v>
+        <v>2.468238</v>
       </c>
       <c r="I362" s="5" t="n">
-        <v>-0.019933</v>
+        <v>1.487267</v>
       </c>
       <c r="J362" t="inlineStr">
         <is>
@@ -29140,24 +29074,28 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>General and administrative expenses (Note 16)</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E363" s="5" t="n">
-        <v>0.000482</v>
-      </c>
-      <c r="F363" s="5" t="n">
-        <v>0.000382</v>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
@@ -29165,10 +29103,10 @@
         </is>
       </c>
       <c r="H363" s="5" t="n">
-        <v>0.001346</v>
+        <v>2.835272</v>
       </c>
       <c r="I363" s="5" t="n">
-        <v>0.002623</v>
+        <v>2.491108</v>
       </c>
       <c r="J363" t="inlineStr">
         <is>
@@ -29204,24 +29142,24 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Loss before other items</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E364" s="5" t="n">
-        <v>0.0025</v>
+        <v>-2.858595</v>
       </c>
       <c r="F364" s="5" t="n">
-        <v>0.052542</v>
+        <v>-2.282645</v>
       </c>
       <c r="G364" t="inlineStr">
         <is>
@@ -29229,10 +29167,10 @@
         </is>
       </c>
       <c r="H364" s="5" t="n">
-        <v>0.000278</v>
+        <v>-0.367034</v>
       </c>
       <c r="I364" s="5" t="n">
-        <v>0.02085</v>
+        <v>-1.003841</v>
       </c>
       <c r="J364" t="inlineStr">
         <is>
@@ -29273,12 +29211,14 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Write off marketable securities (Note 6)</t>
+          <t>Equity loss from investment in associates (Note 7)</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
-      <c r="E365" s="5" t="n">
-        <v>-0.61685</v>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29290,13 +29230,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H365" s="5" t="n">
+        <v>-0.026008</v>
       </c>
       <c r="I365" s="5" t="n">
-        <v>-0.182074</v>
+        <v>-0.156582</v>
       </c>
       <c r="J365" t="inlineStr">
         <is>
@@ -29337,10 +29275,14 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on investments in public</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr"/>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -29357,10 +29299,12 @@
         </is>
       </c>
       <c r="H366" s="5" t="n">
-        <v>-5.235542</v>
-      </c>
-      <c r="I366" s="5" t="n">
-        <v>1.783055</v>
+        <v>5e-06</v>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
@@ -29396,24 +29340,20 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>companies</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Loss on sale of investment</t>
+          <t>Gain on purchase of debt</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E367" s="5" t="n">
+        <v>0.46623</v>
+      </c>
+      <c r="F367" s="5" t="n">
+        <v>0.733331</v>
       </c>
       <c r="G367" t="inlineStr">
         <is>
@@ -29421,10 +29361,12 @@
         </is>
       </c>
       <c r="H367" s="5" t="n">
-        <v>-0.196306</v>
-      </c>
-      <c r="I367" s="5" t="n">
-        <v>-3.253832</v>
+        <v>0.000648</v>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
@@ -29460,12 +29402,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>companies</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Unrealized loss on promissory notes receivable</t>
+          <t>Gain on settlement of debt (Note 20)</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -29485,7 +29427,7 @@
         </is>
       </c>
       <c r="H368" s="5" t="n">
-        <v>-0.148125</v>
+        <v>0.05475</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -29524,10 +29466,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr"/>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Unrealized gain on investment in</t>
+          <t>Income from sale of software (Note 21)</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -29547,10 +29493,12 @@
         </is>
       </c>
       <c r="H369" s="5" t="n">
-        <v>0.292413</v>
-      </c>
-      <c r="I369" s="5" t="n">
-        <v>0.067181</v>
+        <v>0.135321</v>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
@@ -29586,12 +29534,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>private companies</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>private companies total</t>
+          <t>Impairment of mineral properties (Note 12)</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -29611,10 +29559,10 @@
         </is>
       </c>
       <c r="H370" s="5" t="n">
-        <v>-5.255885</v>
+        <v>-0.134665</v>
       </c>
       <c r="I370" s="5" t="n">
-        <v>-1.738712</v>
+        <v>-0.019933</v>
       </c>
       <c r="J370" t="inlineStr">
         <is>
@@ -29650,28 +29598,24 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>private companies</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E371" s="5" t="n">
+        <v>0.000482</v>
+      </c>
+      <c r="F371" s="5" t="n">
+        <v>0.000382</v>
       </c>
       <c r="G371" t="inlineStr">
         <is>
@@ -29679,10 +29623,10 @@
         </is>
       </c>
       <c r="H371" s="5" t="n">
-        <v>-5.622919</v>
+        <v>0.001346</v>
       </c>
       <c r="I371" s="5" t="n">
-        <v>-2.742553</v>
+        <v>0.002623</v>
       </c>
       <c r="J371" t="inlineStr">
         <is>
@@ -29718,28 +29662,24 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>private companies</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E372" s="5" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="F372" s="5" t="n">
+        <v>0.052542</v>
       </c>
       <c r="G372" t="inlineStr">
         <is>
@@ -29747,10 +29687,10 @@
         </is>
       </c>
       <c r="H372" s="5" t="n">
-        <v>-3.7e-07</v>
+        <v>0.000278</v>
       </c>
       <c r="I372" s="5" t="n">
-        <v>-1.7e-07</v>
+        <v>0.02085</v>
       </c>
       <c r="J372" t="inlineStr">
         <is>
@@ -29786,23 +29726,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Write off marketable securities (Note 6)</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" s="5" t="n">
+        <v>-0.61685</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29814,11 +29748,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H373" s="5" t="n">
-        <v>15.394483</v>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I373" s="5" t="n">
-        <v>15.891908</v>
+        <v>-0.182074</v>
       </c>
       <c r="J373" t="inlineStr">
         <is>
@@ -29854,19 +29790,15 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Diluted</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
+          <t>Unrealized gain (loss) on investments in public</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -29883,10 +29815,10 @@
         </is>
       </c>
       <c r="H374" s="5" t="n">
-        <v>15.394483</v>
+        <v>-5.235542</v>
       </c>
       <c r="I374" s="5" t="n">
-        <v>15.891908</v>
+        <v>1.783055</v>
       </c>
       <c r="J374" t="inlineStr">
         <is>
@@ -29922,35 +29854,35 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>companies</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Loss on sale of investments</t>
+          <t>Loss on sale of investment</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
-      <c r="E375" s="5" t="n">
-        <v>-1.634448</v>
-      </c>
-      <c r="F375" s="5" t="n">
-        <v>-1.955638</v>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H375" s="5" t="n">
+        <v>-0.196306</v>
+      </c>
+      <c r="I375" s="5" t="n">
+        <v>-3.253832</v>
       </c>
       <c r="J375" t="inlineStr">
         <is>
@@ -29986,30 +29918,32 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>companies</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Income from property sales</t>
+          <t>Unrealized loss on promissory notes receivable</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
-      <c r="E376" s="5" t="n">
-        <v>0.299381</v>
-      </c>
-      <c r="F376" s="5" t="n">
-        <v>0.310313</v>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H376" s="5" t="n">
+        <v>-0.148125</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -30048,41 +29982,33 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B377" t="inlineStr"/>
       <c r="C377" t="inlineStr">
         <is>
-          <t>General and administrative expenses (Note 19)</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E377" s="5" t="n">
-        <v>3.120729</v>
-      </c>
-      <c r="F377" s="5" t="n">
-        <v>2.610964</v>
+          <t>Unrealized gain on investment in</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H377" s="5" t="n">
+        <v>0.292413</v>
+      </c>
+      <c r="I377" s="5" t="n">
+        <v>0.067181</v>
       </c>
       <c r="J377" t="inlineStr">
         <is>
@@ -30118,39 +30044,35 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>private companies</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E378" s="5" t="n">
-        <v>-5.1e-05</v>
-      </c>
-      <c r="F378" s="5" t="n">
-        <v>0.000191</v>
+          <t>private companies total</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H378" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I378" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H378" s="5" t="n">
+        <v>-5.255885</v>
+      </c>
+      <c r="I378" s="5" t="n">
+        <v>-1.738712</v>
       </c>
       <c r="J378" t="inlineStr">
         <is>
@@ -30186,35 +30108,39 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>private companies</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Penalties and interest</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
-      <c r="E379" s="5" t="n">
-        <v>-0.0001</v>
-      </c>
-      <c r="F379" s="5" t="n">
-        <v>-0.0012</v>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H379" s="5" t="n">
+        <v>-5.622919</v>
+      </c>
+      <c r="I379" s="5" t="n">
+        <v>-2.742553</v>
       </c>
       <c r="J379" t="inlineStr">
         <is>
@@ -30250,37 +30176,39 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>private companies</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Bad debts</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr"/>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F380" s="5" t="n">
-        <v>-0.047619</v>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H380" s="5" t="n">
+        <v>-3.7e-07</v>
+      </c>
+      <c r="I380" s="5" t="n">
+        <v>-1.7e-07</v>
       </c>
       <c r="J380" t="inlineStr">
         <is>
@@ -30316,35 +30244,39 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Equity loss of affiliates (Note 7)</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr"/>
-      <c r="E381" s="5" t="n">
-        <v>-0.096304</v>
-      </c>
-      <c r="F381" s="5" t="n">
-        <v>-0.03375</v>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H381" s="5" t="n">
+        <v>15.394483</v>
+      </c>
+      <c r="I381" s="5" t="n">
+        <v>15.891908</v>
       </c>
       <c r="J381" t="inlineStr">
         <is>
@@ -30380,35 +30312,39 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Impairment of mineral properties (Note 8)</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
-      <c r="E382" s="5" t="n">
-        <v>-0.338687</v>
-      </c>
-      <c r="F382" s="5" t="n">
-        <v>-0.028843</v>
+          <t>Diluted</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H382" s="5" t="n">
+        <v>15.394483</v>
+      </c>
+      <c r="I382" s="5" t="n">
+        <v>15.891908</v>
       </c>
       <c r="J382" t="inlineStr">
         <is>
@@ -30444,20 +30380,20 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Unrealized gain on investments</t>
+          <t>Loss on sale of investments</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
       <c r="E383" s="5" t="n">
-        <v>1.950089</v>
+        <v>-1.634448</v>
       </c>
       <c r="F383" s="5" t="n">
-        <v>1.405829</v>
+        <v>-1.955638</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
@@ -30508,20 +30444,20 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Other items total</t>
+          <t>Income from property sales</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
       <c r="E384" s="5" t="n">
-        <v>1.367309</v>
+        <v>0.299381</v>
       </c>
       <c r="F384" s="5" t="n">
-        <v>2.080863</v>
+        <v>0.310313</v>
       </c>
       <c r="G384" t="inlineStr">
         <is>
@@ -30572,24 +30508,24 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
+          <t>General and administrative expenses (Note 19)</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E385" s="5" t="n">
-        <v>-1.491286</v>
+        <v>3.120729</v>
       </c>
       <c r="F385" s="5" t="n">
-        <v>-0.201782</v>
+        <v>2.610964</v>
       </c>
       <c r="G385" t="inlineStr">
         <is>
@@ -30640,22 +30576,24 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Current taxes recovery (expense)</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E386" s="5" t="n">
-        <v>0.114017</v>
-      </c>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.1e-05</v>
+      </c>
+      <c r="F386" s="5" t="n">
+        <v>0.000191</v>
       </c>
       <c r="G386" t="inlineStr">
         <is>
@@ -30706,22 +30644,20 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Deferred taxes recovery (expense)</t>
+          <t>Penalties and interest</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
-      <c r="E387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E387" s="5" t="n">
+        <v>-0.0001</v>
       </c>
       <c r="F387" s="5" t="n">
-        <v>-0.008354</v>
+        <v>-0.0012</v>
       </c>
       <c r="G387" t="inlineStr">
         <is>
@@ -30772,20 +30708,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Income taxes total</t>
+          <t>Bad debts</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
-      <c r="E388" s="5" t="n">
-        <v>0.114017</v>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F388" s="5" t="n">
-        <v>-0.008354</v>
+        <v>-0.047619</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
@@ -30836,24 +30774,20 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Equity loss of affiliates (Note 7)</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" s="5" t="n">
-        <v>-1.377269</v>
+        <v>-0.096304</v>
       </c>
       <c r="F389" s="5" t="n">
-        <v>-0.210136</v>
+        <v>-0.03375</v>
       </c>
       <c r="G389" t="inlineStr">
         <is>
@@ -30904,20 +30838,20 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Basic loss per share $</t>
+          <t>Impairment of mineral properties (Note 8)</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
       <c r="E390" s="5" t="n">
-        <v>-1.1e-07</v>
+        <v>-0.338687</v>
       </c>
       <c r="F390" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.028843</v>
       </c>
       <c r="G390" t="inlineStr">
         <is>
@@ -30968,20 +30902,20 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Diluted loss per share $</t>
+          <t>Unrealized gain on investments</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
       <c r="E391" s="5" t="n">
-        <v>-1.1e-07</v>
+        <v>1.950089</v>
       </c>
       <c r="F391" s="5" t="n">
-        <v>-1e-08</v>
+        <v>1.405829</v>
       </c>
       <c r="G391" t="inlineStr">
         <is>
@@ -31032,24 +30966,20 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>- basic</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Other items total</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
       <c r="E392" s="5" t="n">
-        <v>12.132539</v>
+        <v>1.367309</v>
       </c>
       <c r="F392" s="5" t="n">
-        <v>14.302383</v>
+        <v>2.080863</v>
       </c>
       <c r="G392" t="inlineStr">
         <is>
@@ -31100,61 +31030,589 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E393" s="5" t="n">
+        <v>-1.491286</v>
+      </c>
+      <c r="F393" s="5" t="n">
+        <v>-0.201782</v>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Current taxes recovery (expense)</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" s="5" t="n">
+        <v>0.114017</v>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Deferred taxes recovery (expense)</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F395" s="5" t="n">
+        <v>-0.008354</v>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Income taxes total</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" s="5" t="n">
+        <v>0.114017</v>
+      </c>
+      <c r="F396" s="5" t="n">
+        <v>-0.008354</v>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E397" s="5" t="n">
+        <v>-1.377269</v>
+      </c>
+      <c r="F397" s="5" t="n">
+        <v>-0.210136</v>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Basic loss per share $</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
+      <c r="E398" s="5" t="n">
+        <v>-1.1e-07</v>
+      </c>
+      <c r="F398" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr"/>
+      <c r="E399" s="5" t="n">
+        <v>-1.1e-07</v>
+      </c>
+      <c r="F399" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
           <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
-      <c r="C393" t="inlineStr">
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>- basic</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E400" s="5" t="n">
+        <v>12.132539</v>
+      </c>
+      <c r="F400" s="5" t="n">
+        <v>14.302383</v>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
         <is>
           <t>- diluted</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr">
+      <c r="D401" t="inlineStr">
         <is>
           <t>DilutedAverageShares</t>
         </is>
       </c>
-      <c r="E393" s="5" t="n">
+      <c r="E401" s="5" t="n">
         <v>12.132539</v>
       </c>
-      <c r="F393" s="5" t="n">
+      <c r="F401" s="5" t="n">
         <v>14.302383</v>
       </c>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N393" t="inlineStr">
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
         <is>
           <t>-</t>
         </is>
